--- a/Unity/Assets/Config/Excel/GemTalentAreaConfig.xlsx
+++ b/Unity/Assets/Config/Excel/GemTalentAreaConfig.xlsx
@@ -11245,7 +11245,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{94780384-2D75-4F80-81BF-9B79E8A08714}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{F91B7742-8412-45E6-A2BD-AB56B71DE968}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11597,7 +11597,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="7">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:3">
